--- a/exports/alyson-org-roster.xlsx
+++ b/exports/alyson-org-roster.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:H97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,10 +421,13 @@
       <c r="G1" t="str">
         <v>Manager</v>
       </c>
+      <c r="H1" t="str">
+        <v>Active</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>rev_exec_bill</v>
+        <v>cint_exec_bill</v>
       </c>
       <c r="B2" t="str">
         <v>Bill</v>
@@ -436,7 +439,7 @@
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>bill@revcloud.com</v>
+        <v>alysonclient@cintara.ai</v>
       </c>
       <c r="F2" t="str">
         <v>Leadership</v>
@@ -444,10 +447,13 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>rev_abdulhanan_revcloud_com_001</v>
+        <v>cint_abdul_hanan_cintara_ai_001</v>
       </c>
       <c r="B3" t="str">
         <v>Abdul Hanan</v>
@@ -459,7 +465,7 @@
         <v>abdul.hanan.ch@live.com</v>
       </c>
       <c r="E3" t="str">
-        <v>abdulhanan@revcloud.com</v>
+        <v>abdul.hanan@cintara.ai</v>
       </c>
       <c r="F3" t="str">
         <v>Experiments</v>
@@ -467,10 +473,13 @@
       <c r="G3" t="str">
         <v>Omer</v>
       </c>
+      <c r="H3" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>rev_raheem_revcloud_com_002</v>
+        <v>cint_raheem_cintara_ai_002</v>
       </c>
       <c r="B4" t="str">
         <v>Abdul Raheem</v>
@@ -482,7 +491,7 @@
         <v>ab.raheem.2187@gmail.com</v>
       </c>
       <c r="E4" t="str">
-        <v>raheem@revcloud.com</v>
+        <v>raheem@cintara.ai</v>
       </c>
       <c r="F4" t="str">
         <v>Checkout</v>
@@ -490,10 +499,13 @@
       <c r="G4" t="str">
         <v>Zaman</v>
       </c>
+      <c r="H4" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>rev_abdullahwaseem_revcloud_com_003</v>
+        <v>cint_abdullah_waseem_cintara_ai_003</v>
       </c>
       <c r="B5" t="str">
         <v>Abdullah Waseem</v>
@@ -505,7 +517,7 @@
         <v>syedabdullahwaseem@gmail.com</v>
       </c>
       <c r="E5" t="str">
-        <v>abdullahwaseem@revcloud.com</v>
+        <v>abdullah.waseem@cintara.ai</v>
       </c>
       <c r="F5" t="str">
         <v>Experiments</v>
@@ -513,13 +525,16 @@
       <c r="G5" t="str">
         <v>Omer</v>
       </c>
+      <c r="H5" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>rev_ahmadbilal_revcloud_com_004</v>
+        <v>cint_bilal_cintara_ai_004</v>
       </c>
       <c r="B6" t="str">
-        <v>Ahmad Bilal</v>
+        <v>Ahmad Bilal Abdul Wahid</v>
       </c>
       <c r="C6" t="str">
         <v>Lahore</v>
@@ -528,18 +543,21 @@
         <v>ahmedbilalmian@gmail.com</v>
       </c>
       <c r="E6" t="str">
-        <v>ahmadbilal@revcloud.com</v>
+        <v>bilal@cintara.ai</v>
       </c>
       <c r="F6" t="str">
         <v>Acquire</v>
       </c>
       <c r="G6" t="str">
-        <v>Arman</v>
+        <v>Bill</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>rev_ahmad_farooq_revcloud_com_005</v>
+        <v>cint_hashim_cintara_ai_005</v>
       </c>
       <c r="B7" t="str">
         <v>Ahmad Hashim Farooq</v>
@@ -551,7 +569,7 @@
         <v>hashimfarooq777@gmail.com</v>
       </c>
       <c r="E7" t="str">
-        <v>ahmad.farooq@revcloud.com</v>
+        <v>hashim@cintara.ai</v>
       </c>
       <c r="F7" t="str">
         <v>Experiments</v>
@@ -559,13 +577,16 @@
       <c r="G7" t="str">
         <v>Omer</v>
       </c>
+      <c r="H7" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>rev_ahsanzafar_revcloud_com_006</v>
+        <v>cint_ahsan_cintara_ai_006</v>
       </c>
       <c r="B8" t="str">
-        <v>Ahsan Zafar</v>
+        <v>Ahsan Zafar Bloach</v>
       </c>
       <c r="C8" t="str">
         <v>Lahore</v>
@@ -574,7 +595,7 @@
         <v>ahsanz639@gmail.com</v>
       </c>
       <c r="E8" t="str">
-        <v>ahsanzafar@revcloud.com</v>
+        <v>ahsan@cintara.ai</v>
       </c>
       <c r="F8" t="str">
         <v>Checkout</v>
@@ -582,10 +603,13 @@
       <c r="G8" t="str">
         <v>Zaman</v>
       </c>
+      <c r="H8" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>rev_ali_hussnain_revcloud_com_007</v>
+        <v>cint_ali_hussnain_cintara_ai_007</v>
       </c>
       <c r="B9" t="str">
         <v>Ali Hussnain</v>
@@ -597,18 +621,21 @@
         <v>ali.hussnainbabar@gmail.com</v>
       </c>
       <c r="E9" t="str">
-        <v>ali.hussnain@revcloud.com</v>
+        <v>ali.hussnain@cintara.ai</v>
       </c>
       <c r="F9" t="str">
         <v>Data Engineering</v>
       </c>
       <c r="G9" t="str">
-        <v>Kumail</v>
+        <v>Omer</v>
+      </c>
+      <c r="H9" t="str">
+        <v>No</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>rev_ameer_hamza_revcloud_com_008</v>
+        <v>cint_hamza_cintara_ai_008</v>
       </c>
       <c r="B10" t="str">
         <v>Ameer Hamza</v>
@@ -620,7 +647,7 @@
         <v>ameer.hamza.nu@gmail.com</v>
       </c>
       <c r="E10" t="str">
-        <v>ameer.hamza@revcloud.com</v>
+        <v>hamza@cintara.ai</v>
       </c>
       <c r="F10" t="str">
         <v>Experiments</v>
@@ -628,10 +655,13 @@
       <c r="G10" t="str">
         <v>Omer</v>
       </c>
+      <c r="H10" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>rev_ameer_revcloud_com_009</v>
+        <v>cint_hamza_cintara_ai_009</v>
       </c>
       <c r="B11" t="str">
         <v>Ameer Hamza Data Engineer</v>
@@ -643,18 +673,21 @@
         <v>ameer692hamza@gmail.com</v>
       </c>
       <c r="E11" t="str">
-        <v>ameer@revcloud.com</v>
+        <v>hamza@cintara.ai</v>
       </c>
       <c r="F11" t="str">
         <v>Data Engineering</v>
       </c>
       <c r="G11" t="str">
-        <v>Kumail</v>
+        <v>Omer/Bill</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>rev_anam_revcloud_com_010</v>
+        <v>cint_anam_cintara_ai_010</v>
       </c>
       <c r="B12" t="str">
         <v>Anam Shahzad</v>
@@ -666,18 +699,21 @@
         <v>anamshahzadkhan309@gmail.com</v>
       </c>
       <c r="E12" t="str">
-        <v>anam@revcloud.com</v>
+        <v>anam@cintara.ai</v>
       </c>
       <c r="F12" t="str">
         <v>Data Engineering</v>
       </c>
       <c r="G12" t="str">
-        <v>Kumail</v>
+        <v>Omer</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>rev_hareem_revcloud_com_011</v>
+        <v>cint_hareem_cintara_ai_011</v>
       </c>
       <c r="B13" t="str">
         <v>Hareem Farooq</v>
@@ -689,7 +725,7 @@
         <v>hareemfarooq.qc@gmail.com</v>
       </c>
       <c r="E13" t="str">
-        <v>hareem@revcloud.com</v>
+        <v>hareem@cintara.ai</v>
       </c>
       <c r="F13" t="str">
         <v>Channel</v>
@@ -697,13 +733,16 @@
       <c r="G13" t="str">
         <v>Atif Ali</v>
       </c>
+      <c r="H13" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>rev_anila_revcloud_com_012</v>
+        <v>cint_anila_cintara_ai_012</v>
       </c>
       <c r="B14" t="str">
-        <v>Anila Riaz</v>
+        <v>Aneela Shahzadi</v>
       </c>
       <c r="C14" t="str">
         <v>Lahore</v>
@@ -712,7 +751,7 @@
         <v>anilashehzadi5@gmail.com</v>
       </c>
       <c r="E14" t="str">
-        <v>anila@revcloud.com</v>
+        <v>anila@cintara.ai</v>
       </c>
       <c r="F14" t="str">
         <v>People Ops</v>
@@ -720,10 +759,13 @@
       <c r="G14" t="str">
         <v>Mohita</v>
       </c>
+      <c r="H14" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>rev_atifali_revcloud_com_013</v>
+        <v>cint_atif_cintara_ai_013</v>
       </c>
       <c r="B15" t="str">
         <v>Atif Ali</v>
@@ -735,7 +777,7 @@
         <v>SayyedMuhammadAtifAli@gmail.com</v>
       </c>
       <c r="E15" t="str">
-        <v>atifali@revcloud.com</v>
+        <v>atif@cintara.ai</v>
       </c>
       <c r="F15" t="str">
         <v>Channel</v>
@@ -743,10 +785,13 @@
       <c r="G15" t="str">
         <v>Atif Ali</v>
       </c>
+      <c r="H15" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>rev_hadia_gull_revcloud_com_014</v>
+        <v>cint_hadia_gull_cintara_ai_014</v>
       </c>
       <c r="B16" t="str">
         <v>Hadia Gull</v>
@@ -758,7 +803,7 @@
         <v>hadiagull03@gmail.com</v>
       </c>
       <c r="E16" t="str">
-        <v>hadia.gull@revcloud.com</v>
+        <v>hadia.gull@cintara.ai</v>
       </c>
       <c r="F16" t="str">
         <v>Checkout</v>
@@ -766,13 +811,16 @@
       <c r="G16" t="str">
         <v>Zaman</v>
       </c>
+      <c r="H16" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>rev_abdullahsaleem_revcloud_com_015</v>
+        <v>cint_abdullah_saleem_cintara_ai_015</v>
       </c>
       <c r="B17" t="str">
-        <v>Abdullah Saleem</v>
+        <v>HAFIZ ABDULLAH SALEEM</v>
       </c>
       <c r="C17" t="str">
         <v>Lahore</v>
@@ -781,18 +829,21 @@
         <v>ha.abdullah.saleem@gmail.com</v>
       </c>
       <c r="E17" t="str">
-        <v>abdullahsaleem@revcloud.com</v>
+        <v>abdullah.saleem@cintara.ai</v>
       </c>
       <c r="F17" t="str">
         <v>Data Engineering</v>
       </c>
       <c r="G17" t="str">
-        <v>Kumail</v>
+        <v>Omer</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>rev_hamza_revcloud_com_016</v>
+        <v>cint_hamza_cintara_ai_016</v>
       </c>
       <c r="B18" t="str">
         <v>Hamza Hassan</v>
@@ -804,7 +855,7 @@
         <v>hamza.hassan.5348@gmail.com</v>
       </c>
       <c r="E18" t="str">
-        <v>hamza@revcloud.com</v>
+        <v>hamza@cintara.ai</v>
       </c>
       <c r="F18" t="str">
         <v>Experiments</v>
@@ -812,10 +863,13 @@
       <c r="G18" t="str">
         <v>Omer</v>
       </c>
+      <c r="H18" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>rev_hanzla_revcloud_com_017</v>
+        <v>cint_hanzla_cintara_ai_017</v>
       </c>
       <c r="B19" t="str">
         <v>Hanzla Saeed</v>
@@ -827,7 +881,7 @@
         <v>hanzlagc@gmail.com</v>
       </c>
       <c r="E19" t="str">
-        <v>hanzla@revcloud.com</v>
+        <v>hanzla@cintara.ai</v>
       </c>
       <c r="F19" t="str">
         <v>Scrum Master</v>
@@ -835,10 +889,13 @@
       <c r="G19" t="str">
         <v>Bill</v>
       </c>
+      <c r="H19" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>rev_hassan_ali_revcloud_com_018</v>
+        <v>cint_hassan_cintara_ai_018</v>
       </c>
       <c r="B20" t="str">
         <v>Hassan Ali</v>
@@ -850,7 +907,7 @@
         <v>pm.hassanali@gmail.com</v>
       </c>
       <c r="E20" t="str">
-        <v>hassan.ali@revcloud.com</v>
+        <v>hassan@cintara.ai</v>
       </c>
       <c r="F20" t="str">
         <v>Experiments</v>
@@ -858,10 +915,13 @@
       <c r="G20" t="str">
         <v>Omer</v>
       </c>
+      <c r="H20" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>rev_irtaza_revcloud_com_019</v>
+        <v>cint_irtaza_cintara_ai_019</v>
       </c>
       <c r="B21" t="str">
         <v>Irtaza Haider</v>
@@ -873,18 +933,21 @@
         <v>irtazahaider1214@gmail.com</v>
       </c>
       <c r="E21" t="str">
-        <v>irtaza@revcloud.com</v>
+        <v>irtaza@cintara.ai</v>
       </c>
       <c r="F21" t="str">
         <v>Data Architect</v>
       </c>
       <c r="G21" t="str">
-        <v>Bill &amp; Omer/Kumail</v>
+        <v>Bill</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>rev_khuzaima_revcloud_com_020</v>
+        <v>cint_khuzaima_cintara_ai_020</v>
       </c>
       <c r="B22" t="str">
         <v>Khuzaima Tofeeq</v>
@@ -896,7 +959,7 @@
         <v>tofeeqkhuzaima@gmail.com</v>
       </c>
       <c r="E22" t="str">
-        <v>khuzaima@revcloud.com</v>
+        <v>khuzaima@cintara.ai</v>
       </c>
       <c r="F22" t="str">
         <v>Experiments</v>
@@ -904,10 +967,13 @@
       <c r="G22" t="str">
         <v>Omer</v>
       </c>
+      <c r="H22" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>rev_meerab_revcloud_com_021</v>
+        <v>cint_meerab_cintara_ai_021</v>
       </c>
       <c r="B23" t="str">
         <v>Meerab Ali</v>
@@ -919,7 +985,7 @@
         <v>meerabali4486@gmail.com</v>
       </c>
       <c r="E23" t="str">
-        <v>meerab@revcloud.com</v>
+        <v>meerab@cintara.ai</v>
       </c>
       <c r="F23" t="str">
         <v>Channel</v>
@@ -927,10 +993,13 @@
       <c r="G23" t="str">
         <v>Atif Ali</v>
       </c>
+      <c r="H23" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>rev_saba_revcloud_com_022</v>
+        <v>cint_saba_cintara_ai_022</v>
       </c>
       <c r="B24" t="str">
         <v>Saba Imran</v>
@@ -942,7 +1011,7 @@
         <v>sabaimran1029@gmail.com</v>
       </c>
       <c r="E24" t="str">
-        <v>saba@revcloud.com</v>
+        <v>saba@cintara.ai</v>
       </c>
       <c r="F24" t="str">
         <v>Channel</v>
@@ -950,10 +1019,13 @@
       <c r="G24" t="str">
         <v>Atif Ali</v>
       </c>
+      <c r="H24" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>rev_minahil_revcloud_com_023</v>
+        <v>cint_minahil_cintara_ai_023</v>
       </c>
       <c r="B25" t="str">
         <v>Minahil Tariq</v>
@@ -965,7 +1037,7 @@
         <v>minahil923@gmail.com</v>
       </c>
       <c r="E25" t="str">
-        <v>minahil@revcloud.com</v>
+        <v>minahil@cintara.ai</v>
       </c>
       <c r="F25" t="str">
         <v>Checkout</v>
@@ -973,10 +1045,13 @@
       <c r="G25" t="str">
         <v>Zaman</v>
       </c>
+      <c r="H25" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>rev_owais_revcloud_com_024</v>
+        <v>cint_awais_cintara_ai_024</v>
       </c>
       <c r="B26" t="str">
         <v>Muhammad Awais</v>
@@ -988,7 +1063,7 @@
         <v>mowais5921@gmail.com</v>
       </c>
       <c r="E26" t="str">
-        <v>owais@revcloud.com</v>
+        <v>awais@cintara.ai</v>
       </c>
       <c r="F26" t="str">
         <v>People Ops</v>
@@ -996,10 +1071,13 @@
       <c r="G26" t="str">
         <v>Mohita</v>
       </c>
+      <c r="H26" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>rev_fawad_revcloud_com_025</v>
+        <v>cint_fawad_cintara_ai_025</v>
       </c>
       <c r="B27" t="str">
         <v>Malik Fouad Waheed</v>
@@ -1011,7 +1089,7 @@
         <v>fouadwaheed@gmail.com</v>
       </c>
       <c r="E27" t="str">
-        <v>fawad@revcloud.com</v>
+        <v>fawad@cintara.ai</v>
       </c>
       <c r="F27" t="str">
         <v>UI</v>
@@ -1019,13 +1097,16 @@
       <c r="G27" t="str">
         <v>Bill &amp; Omer</v>
       </c>
+      <c r="H27" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>rev_huzaifa_zahid_revcloud_com_026</v>
+        <v>cint_huzaifa_cintara_ai_026</v>
       </c>
       <c r="B28" t="str">
-        <v>Huzaifa Zahid</v>
+        <v>Muhammad Huzaifa Zahid</v>
       </c>
       <c r="C28" t="str">
         <v>Lahore</v>
@@ -1034,7 +1115,7 @@
         <v>huzaifazahid87@gmail.com</v>
       </c>
       <c r="E28" t="str">
-        <v>huzaifa.zahid@revcloud.com</v>
+        <v>huzaifa@cintara.ai</v>
       </c>
       <c r="F28" t="str">
         <v>Experiments</v>
@@ -1042,13 +1123,16 @@
       <c r="G28" t="str">
         <v>Omer</v>
       </c>
+      <c r="H28" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>rev_muhammad_revcloud_com_027</v>
+        <v>cint_muhammad_cintara_ai_027</v>
       </c>
       <c r="B29" t="str">
-        <v>Mubashar Ali</v>
+        <v>Muhammad Mubashar Ali</v>
       </c>
       <c r="C29" t="str">
         <v>Lahore</v>
@@ -1057,7 +1141,7 @@
         <v>mubasharjaved3567@gmail.com</v>
       </c>
       <c r="E29" t="str">
-        <v>muhammad@revcloud.com</v>
+        <v>muhammad@cintara.ai</v>
       </c>
       <c r="F29" t="str">
         <v>Checkout</v>
@@ -1065,10 +1149,13 @@
       <c r="G29" t="str">
         <v>Zaman</v>
       </c>
+      <c r="H29" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>rev_sheharyar_revcloud_com_028</v>
+        <v>cint_sheharyar_cintara_ai_028</v>
       </c>
       <c r="B30" t="str">
         <v>Muhammad Sheharyar</v>
@@ -1080,18 +1167,21 @@
         <v>msheharyarqazi@gmail.com</v>
       </c>
       <c r="E30" t="str">
-        <v>sheharyar@revcloud.com</v>
+        <v>sheharyar@cintara.ai</v>
       </c>
       <c r="F30" t="str">
         <v>Data Engineering</v>
       </c>
       <c r="G30" t="str">
-        <v>Kumail</v>
+        <v>Omer</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>rev_ahsan_javed_revcloud_com_029</v>
+        <v>cint_ahsanjaved_cintara_ai_029</v>
       </c>
       <c r="B31" t="str">
         <v>Ahsan Javed</v>
@@ -1103,7 +1193,7 @@
         <v>Ahsan.javed2000@hotmail.com</v>
       </c>
       <c r="E31" t="str">
-        <v>ahsan.javed@revcloud.com</v>
+        <v>ahsanjaved@cintara.ai</v>
       </c>
       <c r="F31" t="str">
         <v>Channel</v>
@@ -1111,13 +1201,16 @@
       <c r="G31" t="str">
         <v>Atif Ali</v>
       </c>
+      <c r="H31" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>rev_uzair_revcloud_com_030</v>
+        <v>cint_uzair_cintara_ai_030</v>
       </c>
       <c r="B32" t="str">
-        <v>Uzair Imtiaz</v>
+        <v>Muhammad Uzair Imtiaz</v>
       </c>
       <c r="C32" t="str">
         <v>Lahore</v>
@@ -1126,7 +1219,7 @@
         <v>uzair.imtyaz@outlook.com</v>
       </c>
       <c r="E32" t="str">
-        <v>uzair@revcloud.com</v>
+        <v>uzair@cintara.ai</v>
       </c>
       <c r="F32" t="str">
         <v>Checkout</v>
@@ -1134,13 +1227,16 @@
       <c r="G32" t="str">
         <v>Zaman</v>
       </c>
+      <c r="H32" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>rev_usama_revcloud_com_031</v>
+        <v>cint_usama_cintara_ai_031</v>
       </c>
       <c r="B33" t="str">
-        <v>Usama Mir</v>
+        <v>Usama Shahzad Mir</v>
       </c>
       <c r="C33" t="str">
         <v>Lahore</v>
@@ -1149,7 +1245,7 @@
         <v>usamamir666@gamil.com</v>
       </c>
       <c r="E33" t="str">
-        <v>usama@revcloud.com</v>
+        <v>usama@cintara.ai</v>
       </c>
       <c r="F33" t="str">
         <v>Channel</v>
@@ -1157,10 +1253,13 @@
       <c r="G33" t="str">
         <v>Atif Ali</v>
       </c>
+      <c r="H33" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>rev_zaman_revcloud_com_032</v>
+        <v>cint_zaman_cintara_ai_032</v>
       </c>
       <c r="B34" t="str">
         <v>Muhammad Zaman</v>
@@ -1172,7 +1271,7 @@
         <v>zamans510@gmail.com</v>
       </c>
       <c r="E34" t="str">
-        <v>zaman@revcloud.com</v>
+        <v>zaman@cintara.ai</v>
       </c>
       <c r="F34" t="str">
         <v>Checkout</v>
@@ -1180,10 +1279,13 @@
       <c r="G34" t="str">
         <v>Bill</v>
       </c>
+      <c r="H34" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>rev_omar_revcloud_com_033</v>
+        <v>cint_omar_cintara_ai_033</v>
       </c>
       <c r="B35" t="str">
         <v>Omar Asmar</v>
@@ -1195,7 +1297,7 @@
         <v>omarasmaryounas@gmail.com</v>
       </c>
       <c r="E35" t="str">
-        <v>omar@revcloud.com</v>
+        <v>omar@cintara.ai</v>
       </c>
       <c r="F35" t="str">
         <v>People Ops</v>
@@ -1203,10 +1305,13 @@
       <c r="G35" t="str">
         <v>Mohita</v>
       </c>
+      <c r="H35" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>rev_omeraffan_revcloud_com_034</v>
+        <v>cint_omer_cintara_ai_034</v>
       </c>
       <c r="B36" t="str">
         <v>Muhammad Omer Affan</v>
@@ -1218,7 +1323,7 @@
         <v>omeraffan@outlook.com</v>
       </c>
       <c r="E36" t="str">
-        <v>omeraffan@revcloud.com</v>
+        <v>omer@cintara.ai</v>
       </c>
       <c r="F36" t="str">
         <v>Data Architect</v>
@@ -1226,10 +1331,13 @@
       <c r="G36" t="str">
         <v>Bill</v>
       </c>
+      <c r="H36" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>rev_rameen_revcloud_com_035</v>
+        <v>cint_rameen_cintara_ai_035</v>
       </c>
       <c r="B37" t="str">
         <v>Rameen Hamid</v>
@@ -1241,7 +1349,7 @@
         <v>rameenhamidd257@gmail.com</v>
       </c>
       <c r="E37" t="str">
-        <v>rameen@revcloud.com</v>
+        <v>rameen@cintara.ai</v>
       </c>
       <c r="F37" t="str">
         <v>Checkout</v>
@@ -1249,13 +1357,16 @@
       <c r="G37" t="str">
         <v>Zaman</v>
       </c>
+      <c r="H37" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>rev_salman_soomro_revcloud_com_036</v>
+        <v>cint_salman_soomro_cintara_ai_036</v>
       </c>
       <c r="B38" t="str">
-        <v>Salman Soomro</v>
+        <v>Muhammad Salman Akhtar Soomro</v>
       </c>
       <c r="C38" t="str">
         <v>Lahore</v>
@@ -1264,7 +1375,7 @@
         <v>salmanakhtar2@gmail.com</v>
       </c>
       <c r="E38" t="str">
-        <v>salman.soomro@revcloud.com</v>
+        <v>salman.soomro@cintara.ai</v>
       </c>
       <c r="F38" t="str">
         <v>Channel</v>
@@ -1272,10 +1383,13 @@
       <c r="G38" t="str">
         <v>Atif Ali</v>
       </c>
+      <c r="H38" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>rev_naveed_gillani_revcloud_com_037</v>
+        <v>cint_naveed_gillani_cintara_ai_037</v>
       </c>
       <c r="B39" t="str">
         <v>Ahmed Naveed Gillani</v>
@@ -1287,7 +1401,7 @@
         <v>ahmednaveed344@gmail.com</v>
       </c>
       <c r="E39" t="str">
-        <v>naveed.gillani@revcloud.com</v>
+        <v>naveed.gillani@cintara.ai</v>
       </c>
       <c r="F39" t="str">
         <v>Channel</v>
@@ -1295,10 +1409,13 @@
       <c r="G39" t="str">
         <v>Atif Ali</v>
       </c>
+      <c r="H39" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>rev_rutaba_revcloud_com_038</v>
+        <v>cint_rutaba_cintara_ai_038</v>
       </c>
       <c r="B40" t="str">
         <v>Rutaba Afzaal</v>
@@ -1310,7 +1427,7 @@
         <v>rutabaafzal47@gmail.com</v>
       </c>
       <c r="E40" t="str">
-        <v>rutaba@revcloud.com</v>
+        <v>rutaba@cintara.ai</v>
       </c>
       <c r="F40" t="str">
         <v>Acquire</v>
@@ -1318,10 +1435,13 @@
       <c r="G40" t="str">
         <v/>
       </c>
+      <c r="H40" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>rev_shanzay_revcloud_com_039</v>
+        <v>cint_shanzay_cintara_ai_039</v>
       </c>
       <c r="B41" t="str">
         <v>Shanzay Tafazzal</v>
@@ -1333,7 +1453,7 @@
         <v>shanzaytafazzal40@gmail.com</v>
       </c>
       <c r="E41" t="str">
-        <v>shanzay@revcloud.com</v>
+        <v>shanzay@cintara.ai</v>
       </c>
       <c r="F41" t="str">
         <v>Acquire</v>
@@ -1341,10 +1461,13 @@
       <c r="G41" t="str">
         <v/>
       </c>
+      <c r="H41" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>rev_shumailzehra_revcloud_com_040</v>
+        <v>cint_shumail_cintara_ai_040</v>
       </c>
       <c r="B42" t="str">
         <v>Shumail Zehra</v>
@@ -1356,21 +1479,24 @@
         <v>syedashumailzehra@gmail.com</v>
       </c>
       <c r="E42" t="str">
-        <v>shumailzehra@revcloud.com</v>
+        <v>shumail@cintara.ai</v>
       </c>
       <c r="F42" t="str">
         <v>Data Engineering</v>
       </c>
       <c r="G42" t="str">
-        <v>Kumail</v>
+        <v>Omer</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>rev_kumail_revcloud_com_041</v>
+        <v>cint_kumail_cintara_ai_041</v>
       </c>
       <c r="B43" t="str">
-        <v>Syed M Kumail</v>
+        <v>Syed Muhammad Kumail</v>
       </c>
       <c r="C43" t="str">
         <v>Lahore</v>
@@ -1379,7 +1505,7 @@
         <v>smkumail14@gmail.com</v>
       </c>
       <c r="E43" t="str">
-        <v>kumail@revcloud.com</v>
+        <v>kumail@cintara.ai</v>
       </c>
       <c r="F43" t="str">
         <v>Data Architect</v>
@@ -1387,10 +1513,13 @@
       <c r="G43" t="str">
         <v>Bill</v>
       </c>
+      <c r="H43" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>rev_talha_revcloud_com_042</v>
+        <v>cint_talha_cintara_ai_042</v>
       </c>
       <c r="B44" t="str">
         <v>Talha Shahid</v>
@@ -1402,7 +1531,7 @@
         <v>talha.cue@gmail.com</v>
       </c>
       <c r="E44" t="str">
-        <v>talha@revcloud.com</v>
+        <v>talha@cintara.ai</v>
       </c>
       <c r="F44" t="str">
         <v>People Ops</v>
@@ -1410,10 +1539,13 @@
       <c r="G44" t="str">
         <v>Mohita</v>
       </c>
+      <c r="H44" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>rev_tehreem_revcloud_com_043</v>
+        <v>cint_tehreem_riaz_cintara_ai_043</v>
       </c>
       <c r="B45" t="str">
         <v>Tehreem Riaz</v>
@@ -1425,18 +1557,21 @@
         <v>tehreemriaz87@gmail.com</v>
       </c>
       <c r="E45" t="str">
-        <v>tehreem@revcloud.com</v>
+        <v>tehreem.riaz@cintara.ai</v>
       </c>
       <c r="F45" t="str">
         <v>Data Engineering</v>
       </c>
       <c r="G45" t="str">
-        <v>Kumail</v>
+        <v>Omer</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>rev_wisha_revcloud_com_044</v>
+        <v>cint_wisha_cintara_ai_044</v>
       </c>
       <c r="B46" t="str">
         <v>Wisha Eman</v>
@@ -1448,7 +1583,7 @@
         <v>eman.wisha@gmail.com</v>
       </c>
       <c r="E46" t="str">
-        <v>wisha@revcloud.com</v>
+        <v>wisha@cintara.ai</v>
       </c>
       <c r="F46" t="str">
         <v>Experiments</v>
@@ -1456,13 +1591,16 @@
       <c r="G46" t="str">
         <v>Omer</v>
       </c>
+      <c r="H46" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>rev_aditya_revcloud_com_045</v>
+        <v>cint_aditya_cintara_ai_045</v>
       </c>
       <c r="B47" t="str">
-        <v>Aditya Joshi</v>
+        <v>Joshi Aditya Ajay</v>
       </c>
       <c r="C47" t="str">
         <v>Pune</v>
@@ -1471,7 +1609,7 @@
         <v>joshiaditya0511@gmail.com</v>
       </c>
       <c r="E47" t="str">
-        <v>aditya@revcloud.com</v>
+        <v>aditya@cintara.ai</v>
       </c>
       <c r="F47" t="str">
         <v>Experiments</v>
@@ -1479,10 +1617,13 @@
       <c r="G47" t="str">
         <v>Omer</v>
       </c>
+      <c r="H47" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>rev_aaradhya_revcloud_com_046</v>
+        <v>cint_aaradhya_cintara_ai_046</v>
       </c>
       <c r="B48" t="str">
         <v>Aaradhya Badal</v>
@@ -1494,7 +1635,7 @@
         <v>aaradhya.badal.btech2022@sitpune.edu.in</v>
       </c>
       <c r="E48" t="str">
-        <v>aaradhya@revcloud.com</v>
+        <v>aaradhya@cintara.ai</v>
       </c>
       <c r="F48" t="str">
         <v>Acquire</v>
@@ -1502,10 +1643,13 @@
       <c r="G48" t="str">
         <v>Arman</v>
       </c>
+      <c r="H48" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>rev_arman_revcloud_com_047</v>
+        <v>cint_arman_cintara_ai_047</v>
       </c>
       <c r="B49" t="str">
         <v>Arman Verma</v>
@@ -1517,7 +1661,7 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>arman@revcloud.com</v>
+        <v>arman@cintara.ai</v>
       </c>
       <c r="F49" t="str">
         <v>Acquire</v>
@@ -1525,10 +1669,13 @@
       <c r="G49" t="str">
         <v>Bill</v>
       </c>
+      <c r="H49" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>rev_mohita_revcloud_com_048</v>
+        <v>cint_mohita_cintara_ai_048</v>
       </c>
       <c r="B50" t="str">
         <v>Mohita Yadav</v>
@@ -1540,7 +1687,7 @@
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>mohita@revcloud.com</v>
+        <v>mohita@cintara.ai</v>
       </c>
       <c r="F50" t="str">
         <v>People Ops</v>
@@ -1548,13 +1695,16 @@
       <c r="G50" t="str">
         <v>Bill</v>
       </c>
+      <c r="H50" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>rev_bhupendra_contentcognition_net_049</v>
+        <v>cint_bhupen_cintara_ai_049</v>
       </c>
       <c r="B51" t="str">
-        <v>Bhupen Patel</v>
+        <v>Bhupendra Chainsingh Patel</v>
       </c>
       <c r="C51" t="str">
         <v>Pune</v>
@@ -1563,7 +1713,7 @@
         <v>bhupen.patel505@gmail.com</v>
       </c>
       <c r="E51" t="str">
-        <v>bhupendra@contentcognition.net</v>
+        <v>bhupen@cintara.ai</v>
       </c>
       <c r="F51" t="str">
         <v>Affiliate</v>
@@ -1571,10 +1721,13 @@
       <c r="G51" t="str">
         <v>Arman</v>
       </c>
+      <c r="H51" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>rev_yash_contentcognition_net_050</v>
+        <v>cint_yash_cintara_ai_050</v>
       </c>
       <c r="B52" t="str">
         <v>Yash Patel</v>
@@ -1586,7 +1739,7 @@
         <v>ypat6988@gmail.com</v>
       </c>
       <c r="E52" t="str">
-        <v>yash@contentcognition.net</v>
+        <v>yash@cintara.ai</v>
       </c>
       <c r="F52" t="str">
         <v>Acquire</v>
@@ -1594,10 +1747,13 @@
       <c r="G52" t="str">
         <v>Arman</v>
       </c>
+      <c r="H52" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>rev_sahil_revcloud_com_051</v>
+        <v>cint_sahil_divekar_cintara_ai_051</v>
       </c>
       <c r="B53" t="str">
         <v>Sahil Divekar</v>
@@ -1609,7 +1765,7 @@
         <v>sahil.divekar99@gmail.com</v>
       </c>
       <c r="E53" t="str">
-        <v>sahil@revcloud.com</v>
+        <v>sahil.divekar@cintara.ai</v>
       </c>
       <c r="F53" t="str">
         <v>Acquire</v>
@@ -1617,13 +1773,16 @@
       <c r="G53" t="str">
         <v>Arman</v>
       </c>
+      <c r="H53" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>rev_azhar_revcloud_com_052</v>
+        <v>cint_azhar_cintara_ai_052</v>
       </c>
       <c r="B54" t="str">
-        <v>Azhar Sayed</v>
+        <v>Azhar Ismail Sayed</v>
       </c>
       <c r="C54" t="str">
         <v>Pune</v>
@@ -1632,7 +1791,7 @@
         <v>AzharSayed70@gmail.com</v>
       </c>
       <c r="E54" t="str">
-        <v>azhar@revcloud.com</v>
+        <v>azhar@cintara.ai</v>
       </c>
       <c r="F54" t="str">
         <v>Affiliate</v>
@@ -1640,10 +1799,13 @@
       <c r="G54" t="str">
         <v>Arman</v>
       </c>
+      <c r="H54" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>rev_piyush_revcloud_com_053</v>
+        <v>cint_piyush_cintara_ai_053</v>
       </c>
       <c r="B55" t="str">
         <v>Piyush Parkhe</v>
@@ -1655,7 +1817,7 @@
         <v>piyushparkhe@gmail.com</v>
       </c>
       <c r="E55" t="str">
-        <v>piyush@revcloud.com</v>
+        <v>piyush@cintara.ai</v>
       </c>
       <c r="F55" t="str">
         <v>Growth Team</v>
@@ -1663,13 +1825,16 @@
       <c r="G55" t="str">
         <v>Arman</v>
       </c>
+      <c r="H55" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>rev_thirumalai_revcloud_com_054</v>
+        <v>cint_thirumalai_cintara_ai_054</v>
       </c>
       <c r="B56" t="str">
-        <v>Thirumalainambi Maahraja</v>
+        <v>YADAVAR THIRUMALAINAMBI MAHARAJA</v>
       </c>
       <c r="C56" t="str">
         <v>Pune</v>
@@ -1678,7 +1843,7 @@
         <v>mthirumalai2905@gmail.com</v>
       </c>
       <c r="E56" t="str">
-        <v>thirumalai@revcloud.com</v>
+        <v>thirumalai@cintara.ai</v>
       </c>
       <c r="F56" t="str">
         <v>Experiments</v>
@@ -1686,13 +1851,16 @@
       <c r="G56" t="str">
         <v>Omer</v>
       </c>
+      <c r="H56" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>rev_om_podey_revcloud_com_055</v>
+        <v>cint_om_podey_cintara_ai_055</v>
       </c>
       <c r="B57" t="str">
-        <v>Om Podey</v>
+        <v>Om Prabhakar Podey</v>
       </c>
       <c r="C57" t="str">
         <v>Pune</v>
@@ -1701,7 +1869,7 @@
         <v>ompodey@gmail.com</v>
       </c>
       <c r="E57" t="str">
-        <v>om.podey@revcloud.com</v>
+        <v>om.podey@cintara.ai</v>
       </c>
       <c r="F57" t="str">
         <v>HomeLight</v>
@@ -1709,13 +1877,16 @@
       <c r="G57" t="str">
         <v>Arman</v>
       </c>
+      <c r="H57" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>rev_vyankatesh_revcloud_com_056</v>
+        <v>cint_vyankatesh_cintara_ai_056</v>
       </c>
       <c r="B58" t="str">
-        <v>Vyankatesh Pete</v>
+        <v>Vyankatesh Dnyanoba Pete</v>
       </c>
       <c r="C58" t="str">
         <v>Pune</v>
@@ -1724,7 +1895,7 @@
         <v>vyankatesh.pete@gmail.com</v>
       </c>
       <c r="E58" t="str">
-        <v>vyankatesh@revcloud.com</v>
+        <v>vyankatesh@cintara.ai</v>
       </c>
       <c r="F58" t="str">
         <v>Acquire</v>
@@ -1732,10 +1903,13 @@
       <c r="G58" t="str">
         <v>Arman</v>
       </c>
+      <c r="H58" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>rev_garima_revcloud_com_057</v>
+        <v>cint_garima_cintara_ai_057</v>
       </c>
       <c r="B59" t="str">
         <v>Garima Singh</v>
@@ -1747,7 +1921,7 @@
         <v>garimasingh130197@gmail.com</v>
       </c>
       <c r="E59" t="str">
-        <v>garima@revcloud.com</v>
+        <v>garima@cintara.ai</v>
       </c>
       <c r="F59" t="str">
         <v>People Ops</v>
@@ -1755,10 +1929,13 @@
       <c r="G59" t="str">
         <v>Mohita</v>
       </c>
+      <c r="H59" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>rev_bhumika_revcloud_com_058</v>
+        <v>cint_bhumika_cintara_ai_058</v>
       </c>
       <c r="B60" t="str">
         <v>Bhumikaben Rikhilkumar Kyada</v>
@@ -1770,7 +1947,7 @@
         <v>bhumikagondaliya24@gmail.com</v>
       </c>
       <c r="E60" t="str">
-        <v>bhumika@revcloud.com</v>
+        <v>bhumika@cintara.ai</v>
       </c>
       <c r="F60" t="str">
         <v>People Ops</v>
@@ -1778,10 +1955,13 @@
       <c r="G60" t="str">
         <v>Mohita</v>
       </c>
+      <c r="H60" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>rev_sakshi_revcloud_com_059</v>
+        <v>cint_sakshi_cintara_ai_059</v>
       </c>
       <c r="B61" t="str">
         <v>Sakshi Choudhary</v>
@@ -1793,7 +1973,7 @@
         <v>choudharysakshi551@gmail.com</v>
       </c>
       <c r="E61" t="str">
-        <v>sakshi@revcloud.com</v>
+        <v>sakshi@cintara.ai</v>
       </c>
       <c r="F61" t="str">
         <v>People Ops</v>
@@ -1801,10 +1981,13 @@
       <c r="G61" t="str">
         <v>Mohita</v>
       </c>
+      <c r="H61" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>rev_aditya_singh_revcloud_com_060</v>
+        <v>cint_aditya_singh_cintara_ai_060</v>
       </c>
       <c r="B62" t="str">
         <v>Aditya Singh</v>
@@ -1816,7 +1999,7 @@
         <v>adityavishalsingh@gmail.com</v>
       </c>
       <c r="E62" t="str">
-        <v>aditya.singh@revcloud.com</v>
+        <v>aditya.singh@cintara.ai</v>
       </c>
       <c r="F62" t="str">
         <v>People Ops</v>
@@ -1824,13 +2007,16 @@
       <c r="G62" t="str">
         <v>Mohita</v>
       </c>
+      <c r="H62" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>rev_saif_revcloud_com_061</v>
+        <v>cint_saif_tamboli_cintara_ai_061</v>
       </c>
       <c r="B63" t="str">
-        <v>Saif Tamboli</v>
+        <v>Saif Rafik Tamboli</v>
       </c>
       <c r="C63" t="str">
         <v>Pune</v>
@@ -1839,7 +2025,7 @@
         <v>tambolisaif13@gmail.com</v>
       </c>
       <c r="E63" t="str">
-        <v>saif@revcloud.com</v>
+        <v>saif.tamboli@cintara.ai</v>
       </c>
       <c r="F63" t="str">
         <v>Affiliate</v>
@@ -1847,22 +2033,25 @@
       <c r="G63" t="str">
         <v>Arman</v>
       </c>
+      <c r="H63" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>rev_asmita_revcloud_com_062</v>
+        <v>cint_aryaman_cintara_ai_062</v>
       </c>
       <c r="B64" t="str">
-        <v>Asmita Amritraj</v>
+        <v>Aryaman Singh</v>
       </c>
       <c r="C64" t="str">
         <v>Pune</v>
       </c>
       <c r="D64" t="str">
-        <v>asmitaamritraj@gmail.com</v>
+        <v/>
       </c>
       <c r="E64" t="str">
-        <v>asmita@revcloud.com</v>
+        <v>aryaman@cintara.ai</v>
       </c>
       <c r="F64" t="str">
         <v>Affiliate</v>
@@ -1870,68 +2059,77 @@
       <c r="G64" t="str">
         <v>Arman</v>
       </c>
+      <c r="H64" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>rev_sabtain_revcloud_com_063</v>
+        <v>cint_asmita_amritraj_cintara_ai_063</v>
       </c>
       <c r="B65" t="str">
-        <v>Sabtain Ashiq</v>
+        <v>Asmita Amritraj</v>
       </c>
       <c r="C65" t="str">
-        <v>Bahawalpur</v>
+        <v>Pune</v>
       </c>
       <c r="D65" t="str">
-        <v>djsubtain@gmail.com</v>
+        <v>asmitaamritraj@gmail.com</v>
       </c>
       <c r="E65" t="str">
-        <v>sabtain@revcloud.com</v>
+        <v>asmita.amritraj@cintara.ai</v>
       </c>
       <c r="F65" t="str">
-        <v>Sourcer</v>
+        <v>Affiliate</v>
       </c>
       <c r="G65" t="str">
-        <v>Mohita</v>
+        <v>Arman</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>rev_rana_revcloud_com_064</v>
+        <v>cint_sabtain_cintara_ai_064</v>
       </c>
       <c r="B66" t="str">
-        <v>Rana Ali</v>
+        <v>Sabtain Ashiq</v>
       </c>
       <c r="C66" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D66" t="str">
-        <v>ranaalishabbir9@gmail.com</v>
+        <v>djsubtain@gmail.com</v>
       </c>
       <c r="E66" t="str">
-        <v>rana@revcloud.com</v>
+        <v>sabtain@cintara.ai</v>
       </c>
       <c r="F66" t="str">
         <v>Sourcer</v>
       </c>
       <c r="G66" t="str">
-        <v>Sabtain</v>
+        <v>Mohita</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>rev_abdullah_revcloud_com_065</v>
+        <v>cint_rana_cintara_ai_065</v>
       </c>
       <c r="B67" t="str">
-        <v>Abdullah Raheem</v>
+        <v>Rana Ali</v>
       </c>
       <c r="C67" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D67" t="str">
-        <v/>
+        <v>ranaalishabbir9@gmail.com</v>
       </c>
       <c r="E67" t="str">
-        <v>abdullah@revcloud.com</v>
+        <v>rana@cintara.ai</v>
       </c>
       <c r="F67" t="str">
         <v>Sourcer</v>
@@ -1939,22 +2137,25 @@
       <c r="G67" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H67" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>rev_adeel_revcloud_com_066</v>
+        <v>cint_abdullah_cintara_ai_066</v>
       </c>
       <c r="B68" t="str">
-        <v>Adeel Shakir</v>
+        <v>Abdullah Raheem</v>
       </c>
       <c r="C68" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D68" t="str">
-        <v>adeelshakir356@gmail.com</v>
+        <v/>
       </c>
       <c r="E68" t="str">
-        <v>adeel@revcloud.com</v>
+        <v>abdullah@cintara.ai</v>
       </c>
       <c r="F68" t="str">
         <v>Sourcer</v>
@@ -1962,22 +2163,25 @@
       <c r="G68" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H68" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>rev_ahsan_revcloud_com_067</v>
+        <v>cint_adeel_cintara_ai_067</v>
       </c>
       <c r="B69" t="str">
-        <v>Ahsan Raza</v>
+        <v>Adeel Shakir</v>
       </c>
       <c r="C69" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D69" t="str">
-        <v>malikahsanraza05@gmail.com</v>
+        <v>adeelshakir356@gmail.com</v>
       </c>
       <c r="E69" t="str">
-        <v>ahsan@revcloud.com</v>
+        <v>adeel@cintara.ai</v>
       </c>
       <c r="F69" t="str">
         <v>Sourcer</v>
@@ -1985,22 +2189,25 @@
       <c r="G69" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H69" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>rev_ali_revcloud_com_068</v>
+        <v>cint_ahsan_cintara_ai_068</v>
       </c>
       <c r="B70" t="str">
-        <v>Ali Raza</v>
+        <v>Ahsan Raza</v>
       </c>
       <c r="C70" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>malikahsanraza05@gmail.com</v>
       </c>
       <c r="E70" t="str">
-        <v>ali@revcloud.com</v>
+        <v>ahsan@cintara.ai</v>
       </c>
       <c r="F70" t="str">
         <v>Sourcer</v>
@@ -2008,13 +2215,16 @@
       <c r="G70" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H70" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>rev_alisheeraz_revcloud_com_069</v>
+        <v>cint_ali_cintara_ai_069</v>
       </c>
       <c r="B71" t="str">
-        <v>Ali Sheraz</v>
+        <v>Ali Raza</v>
       </c>
       <c r="C71" t="str">
         <v>Bahawalpur</v>
@@ -2023,7 +2233,7 @@
         <v/>
       </c>
       <c r="E71" t="str">
-        <v>alisheeraz@revcloud.com</v>
+        <v>ali@cintara.ai</v>
       </c>
       <c r="F71" t="str">
         <v>Sourcer</v>
@@ -2031,22 +2241,25 @@
       <c r="G71" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H71" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>rev_arooj_revcloud_com_070</v>
+        <v>cint_alisheeraz_cintara_ai_070</v>
       </c>
       <c r="B72" t="str">
-        <v>Arooj Fatima</v>
+        <v>Ali Sheraz</v>
       </c>
       <c r="C72" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D72" t="str">
-        <v>aroojf5366@gmail.com</v>
+        <v/>
       </c>
       <c r="E72" t="str">
-        <v>arooj@revcloud.com</v>
+        <v>alisheeraz@cintara.ai</v>
       </c>
       <c r="F72" t="str">
         <v>Sourcer</v>
@@ -2054,22 +2267,25 @@
       <c r="G72" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H72" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>rev_ayeshaiqbal_revcloud_com_071</v>
+        <v>cint_arooj_cintara_ai_071</v>
       </c>
       <c r="B73" t="str">
-        <v>Ayesha Iqbal</v>
+        <v>Arooj Fatima</v>
       </c>
       <c r="C73" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D73" t="str">
-        <v/>
+        <v>aroojf5366@gmail.com</v>
       </c>
       <c r="E73" t="str">
-        <v>ayeshaiqbal@revcloud.com</v>
+        <v>arooj@cintara.ai</v>
       </c>
       <c r="F73" t="str">
         <v>Sourcer</v>
@@ -2077,13 +2293,16 @@
       <c r="G73" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H73" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>rev_hina_revcloud_com_072</v>
+        <v>cint_ayesha_cintara_ai_072</v>
       </c>
       <c r="B74" t="str">
-        <v>Hina Samreen</v>
+        <v>Ayesha Iqbal</v>
       </c>
       <c r="C74" t="str">
         <v>Bahawalpur</v>
@@ -2092,7 +2311,7 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>hina@revcloud.com</v>
+        <v>ayesha@cintara.ai</v>
       </c>
       <c r="F74" t="str">
         <v>Sourcer</v>
@@ -2100,22 +2319,25 @@
       <c r="G74" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H74" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>rev_husnain_revcloud_com_073</v>
+        <v>cint_hina_cintara_ai_073</v>
       </c>
       <c r="B75" t="str">
-        <v>Husnain Ali</v>
+        <v>Hina Samreen</v>
       </c>
       <c r="C75" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D75" t="str">
-        <v>husnainali8087@gmail.com</v>
+        <v/>
       </c>
       <c r="E75" t="str">
-        <v>husnain@revcloud.com</v>
+        <v>hina@cintara.ai</v>
       </c>
       <c r="F75" t="str">
         <v>Sourcer</v>
@@ -2123,22 +2345,25 @@
       <c r="G75" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H75" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>rev_iqra_revcloud_com_074</v>
+        <v>cint_husnain_cintara_ai_074</v>
       </c>
       <c r="B76" t="str">
-        <v>Iqra Rafique</v>
+        <v>Husnain Ali</v>
       </c>
       <c r="C76" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D76" t="str">
-        <v>iqrasabtain043@gmail.com</v>
+        <v>husnainali8087@gmail.com</v>
       </c>
       <c r="E76" t="str">
-        <v>iqra@revcloud.com</v>
+        <v>husnain@cintara.ai</v>
       </c>
       <c r="F76" t="str">
         <v>Sourcer</v>
@@ -2146,22 +2371,25 @@
       <c r="G76" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H76" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>rev_khawar_revcloud_com_075</v>
+        <v>cint_iqra_cintara_ai_075</v>
       </c>
       <c r="B77" t="str">
-        <v>Khawar Ali</v>
+        <v>Iqra Rafique</v>
       </c>
       <c r="C77" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D77" t="str">
-        <v>khawarali971@gmail.com</v>
+        <v>iqrasabtain043@gmail.com</v>
       </c>
       <c r="E77" t="str">
-        <v>khawar@revcloud.com</v>
+        <v>iqra@cintara.ai</v>
       </c>
       <c r="F77" t="str">
         <v>Sourcer</v>
@@ -2169,22 +2397,25 @@
       <c r="G77" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H77" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>rev_malik_revcloud_com_076</v>
+        <v>cint_alysonclient_cintara_ai_076</v>
       </c>
       <c r="B78" t="str">
-        <v>Malik Asif</v>
+        <v>Khawar Ali</v>
       </c>
       <c r="C78" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D78" t="str">
-        <v>malikasifchannar125@gmail.com</v>
+        <v>khawarali971@gmail.com</v>
       </c>
       <c r="E78" t="str">
-        <v>malik@revcloud.com</v>
+        <v>alysonclient@cintara.ai</v>
       </c>
       <c r="F78" t="str">
         <v>Sourcer</v>
@@ -2192,22 +2423,25 @@
       <c r="G78" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H78" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>rev_mudaser_revcloud_com_077</v>
+        <v>cint_malik_cintara_ai_077</v>
       </c>
       <c r="B79" t="str">
-        <v>Mudassar Rafique</v>
+        <v>Malik Asif</v>
       </c>
       <c r="C79" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D79" t="str">
-        <v>mudasersunny@gmail.com</v>
+        <v>malikasifchannar125@gmail.com</v>
       </c>
       <c r="E79" t="str">
-        <v>mudaser@revcloud.com</v>
+        <v>malik@cintara.ai</v>
       </c>
       <c r="F79" t="str">
         <v>Sourcer</v>
@@ -2215,22 +2449,25 @@
       <c r="G79" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H79" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>rev_muhammadsaqlain_revcloud_com_078</v>
+        <v>cint_mudassar_cintara_ai_078</v>
       </c>
       <c r="B80" t="str">
-        <v>Muhammad Saqlain</v>
+        <v>Mudassar Rafique</v>
       </c>
       <c r="C80" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D80" t="str">
-        <v>msaqlain2900@gmail.com</v>
+        <v>mudasersunny@gmail.com</v>
       </c>
       <c r="E80" t="str">
-        <v>muhammadsaqlain@revcloud.com</v>
+        <v>mudassar@cintara.ai</v>
       </c>
       <c r="F80" t="str">
         <v>Sourcer</v>
@@ -2238,22 +2475,25 @@
       <c r="G80" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H80" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>rev_muhammadt_revcloud_com_079</v>
+        <v>cint_saqlain_cintara_ai_079</v>
       </c>
       <c r="B81" t="str">
-        <v>Muhammad Tahreem</v>
+        <v>Muhammad Saqlain</v>
       </c>
       <c r="C81" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D81" t="str">
-        <v>tahreem2567@gmail.com</v>
+        <v>msaqlain2900@gmail.com</v>
       </c>
       <c r="E81" t="str">
-        <v>muhammadt@revcloud.com</v>
+        <v>saqlain@cintara.ai</v>
       </c>
       <c r="F81" t="str">
         <v>Sourcer</v>
@@ -2261,22 +2501,25 @@
       <c r="G81" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H81" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>rev_no_email_found_080</v>
+        <v>cint_muhammad_tahreem_cintara_ai_080</v>
       </c>
       <c r="B82" t="str">
-        <v>Naveed Ahmmad</v>
+        <v>Muhammad Tahreem</v>
       </c>
       <c r="C82" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D82" t="str">
-        <v/>
+        <v>tahreem2567@gmail.com</v>
       </c>
       <c r="E82" t="str">
-        <v>user80@revcloud.com</v>
+        <v>muhammad.tahreem@cintara.ai</v>
       </c>
       <c r="F82" t="str">
         <v>Sourcer</v>
@@ -2284,13 +2527,16 @@
       <c r="G82" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H82" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>rev_noor_revcloud_com_081</v>
+        <v>cint_user81_cintara_ai_081</v>
       </c>
       <c r="B83" t="str">
-        <v>Noor Ul Aain</v>
+        <v>Naveed Ahmmad</v>
       </c>
       <c r="C83" t="str">
         <v>Bahawalpur</v>
@@ -2299,7 +2545,7 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>noor@revcloud.com</v>
+        <v>No email found</v>
       </c>
       <c r="F83" t="str">
         <v>Sourcer</v>
@@ -2307,13 +2553,16 @@
       <c r="G83" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H83" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>rev_rabia_revcloud_com_082</v>
+        <v>cint_noor_cintara_ai_082</v>
       </c>
       <c r="B84" t="str">
-        <v>Rabia Saher</v>
+        <v>Noor Ul Aain</v>
       </c>
       <c r="C84" t="str">
         <v>Bahawalpur</v>
@@ -2322,7 +2571,7 @@
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>rabia@revcloud.com</v>
+        <v>noor@cintara.ai</v>
       </c>
       <c r="F84" t="str">
         <v>Sourcer</v>
@@ -2330,13 +2579,16 @@
       <c r="G84" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H84" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>rev_no_email_found_083</v>
+        <v>cint_rabia_cintara_ai_083</v>
       </c>
       <c r="B85" t="str">
-        <v>Rimsha Javed</v>
+        <v>Rabia Saher</v>
       </c>
       <c r="C85" t="str">
         <v>Bahawalpur</v>
@@ -2345,7 +2597,7 @@
         <v/>
       </c>
       <c r="E85" t="str">
-        <v>user83@revcloud.com</v>
+        <v>rabia@cintara.ai</v>
       </c>
       <c r="F85" t="str">
         <v>Sourcer</v>
@@ -2353,13 +2605,16 @@
       <c r="G85" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H85" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>rev_sami_revcloud_com_084</v>
+        <v>cint_user84_cintara_ai_084</v>
       </c>
       <c r="B86" t="str">
-        <v>Sami Ullah</v>
+        <v>Rimsha Javed</v>
       </c>
       <c r="C86" t="str">
         <v>Bahawalpur</v>
@@ -2368,7 +2623,7 @@
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>sami@revcloud.com</v>
+        <v>No email found</v>
       </c>
       <c r="F86" t="str">
         <v>Sourcer</v>
@@ -2376,22 +2631,25 @@
       <c r="G86" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H86" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>rev_shabanaali_revcloud_com_085</v>
+        <v>cint_sami_cintara_ai_085</v>
       </c>
       <c r="B87" t="str">
-        <v>Shabana Ali</v>
+        <v>Sami Ullah</v>
       </c>
       <c r="C87" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D87" t="str">
-        <v>shabana.ali1342@gmail.com</v>
+        <v/>
       </c>
       <c r="E87" t="str">
-        <v>shabanaali@revcloud.com</v>
+        <v>sami@cintara.ai</v>
       </c>
       <c r="F87" t="str">
         <v>Sourcer</v>
@@ -2399,22 +2657,25 @@
       <c r="G87" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H87" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>rev_shumaila_revcloud_com_086</v>
+        <v>cint_shabanaali_cintara_ai_086</v>
       </c>
       <c r="B88" t="str">
-        <v>Shumaila Tahir</v>
+        <v>Shabana Ali</v>
       </c>
       <c r="C88" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D88" t="str">
-        <v>shumailaaa22@gmail.com</v>
+        <v>shabana.ali1342@gmail.com</v>
       </c>
       <c r="E88" t="str">
-        <v>shumaila@revcloud.com</v>
+        <v>shabanaali@cintara.ai</v>
       </c>
       <c r="F88" t="str">
         <v>Sourcer</v>
@@ -2422,22 +2683,25 @@
       <c r="G88" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H88" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>rev_muhammadareeb_revcloud_com_087</v>
+        <v>cint_shumaila_cintara_ai_087</v>
       </c>
       <c r="B89" t="str">
-        <v>Muhammad Areeb Abbas</v>
+        <v>Shumaila Tahir</v>
       </c>
       <c r="C89" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D89" t="str">
-        <v>areeb.abbas786@gmail.com</v>
+        <v>shumailaaa22@gmail.com</v>
       </c>
       <c r="E89" t="str">
-        <v>muhammadareeb@revcloud.com</v>
+        <v>shumaila@cintara.ai</v>
       </c>
       <c r="F89" t="str">
         <v>Sourcer</v>
@@ -2445,22 +2709,25 @@
       <c r="G89" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H89" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>rev_muhammadkamran_revcloud_com_088</v>
+        <v>cint_muhammadareeb_cintara_ai_088</v>
       </c>
       <c r="B90" t="str">
-        <v>Muhammad Kamran</v>
+        <v>Muhammad Areeb Abbas</v>
       </c>
       <c r="C90" t="str">
         <v>Bahawalpur</v>
       </c>
       <c r="D90" t="str">
-        <v/>
+        <v>areeb.abbas786@gmail.com</v>
       </c>
       <c r="E90" t="str">
-        <v>muhammadkamran@revcloud.com</v>
+        <v>muhammadareeb@cintara.ai</v>
       </c>
       <c r="F90" t="str">
         <v>Sourcer</v>
@@ -2468,125 +2735,195 @@
       <c r="G90" t="str">
         <v>Sabtain</v>
       </c>
+      <c r="H90" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>rev_prashansa_chauhan_089</v>
+        <v>cint_muhammadkamran_cintara_ai_089</v>
       </c>
       <c r="B91" t="str">
-        <v>Prashansa Chauhan</v>
+        <v>Muhammad Kamran</v>
       </c>
       <c r="C91" t="str">
-        <v>Pune</v>
+        <v>Bahawalpur</v>
       </c>
       <c r="D91" t="str">
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>user89@revcloud.com</v>
+        <v>muhammadkamran@cintara.ai</v>
       </c>
       <c r="F91" t="str">
-        <v>People Ops</v>
+        <v>Sourcer</v>
       </c>
       <c r="G91" t="str">
-        <v>Mohita</v>
+        <v>Sabtain</v>
+      </c>
+      <c r="H91" t="str">
+        <v>No</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>rev_hamza_zafar_090</v>
+        <v>cint_prashansa_cintara_ai_090</v>
       </c>
       <c r="B92" t="str">
-        <v>Hamza Zafar</v>
+        <v>Prashansa Chauhan</v>
       </c>
       <c r="C92" t="str">
-        <v>Lahore</v>
+        <v>Pune</v>
       </c>
       <c r="D92" t="str">
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>user90@revcloud.com</v>
+        <v>prashansa@cintara.ai</v>
       </c>
       <c r="F92" t="str">
-        <v>Acquire</v>
+        <v>People Ops</v>
       </c>
       <c r="G92" t="str">
-        <v>Arman</v>
+        <v>Mohita</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>rev_aryaman_singh_091</v>
+        <v>cint_hamza_zafar_cintara_ai_091</v>
       </c>
       <c r="B93" t="str">
-        <v>Aryaman Singh</v>
+        <v>Hamza Zafar</v>
       </c>
       <c r="C93" t="str">
-        <v>Pune</v>
+        <v>Lahore</v>
       </c>
       <c r="D93" t="str">
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>user91@revcloud.com</v>
+        <v>hamza.zafar@cintara.ai</v>
       </c>
       <c r="F93" t="str">
-        <v>Affiliate</v>
+        <v>Acquire</v>
       </c>
       <c r="G93" t="str">
-        <v>Yash</v>
+        <v>Arman</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>rev_swapnil_thorat_092</v>
+        <v>cint_adil_cintara_ai_092</v>
       </c>
       <c r="B94" t="str">
-        <v>Swapnil Thorat</v>
+        <v>Adil Ahmed</v>
       </c>
       <c r="C94" t="str">
-        <v>Pune</v>
+        <v>Lahore</v>
       </c>
       <c r="D94" t="str">
         <v/>
       </c>
       <c r="E94" t="str">
-        <v>user92@revcloud.com</v>
+        <v>adil@cintara.ai</v>
       </c>
       <c r="F94" t="str">
-        <v>Channel</v>
+        <v>Acquire</v>
       </c>
       <c r="G94" t="str">
         <v>Bill</v>
       </c>
+      <c r="H94" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>rev_rohan_n_093</v>
+        <v>cint_farhan_cintara_ai_093</v>
       </c>
       <c r="B95" t="str">
-        <v>Rohan N</v>
+        <v>Farhan Tariq</v>
       </c>
       <c r="C95" t="str">
-        <v>Pune</v>
+        <v>Lahore</v>
       </c>
       <c r="D95" t="str">
         <v/>
       </c>
       <c r="E95" t="str">
-        <v>user93@revcloud.com</v>
+        <v>farhan@cintara.ai</v>
       </c>
       <c r="F95" t="str">
-        <v>Acquire</v>
+        <v>HomeLight</v>
       </c>
       <c r="G95" t="str">
-        <v>Om</v>
+        <v>Bill</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>cint_aryan_cintara_ai_094</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Aryan Sawant</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Pune</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v>aryan@cintara.ai</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Data Engineering</v>
+      </c>
+      <c r="G96" t="str">
+        <v>Omer</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>cint_vinit_cintara_ai_095</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Vinit Solanki</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Pune</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v>vinit@cintara.ai</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Data Engineering</v>
+      </c>
+      <c r="G97" t="str">
+        <v>Omer</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Yes</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H97"/>
   </ignoredErrors>
 </worksheet>
 </file>